--- a/element_checker_settings.xlsx
+++ b/element_checker_settings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\CODE\Elemer_checker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4254E22C-62CA-497C-9557-6EABD6630DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E48C19C-CCA6-4BE4-9D0E-F04BCF6C5983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1220,7 +1220,7 @@
         <v>74</v>
       </c>
       <c r="F25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
@@ -1242,7 +1242,7 @@
         <v>75</v>
       </c>
       <c r="F26" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
@@ -1264,7 +1264,7 @@
         <v>76</v>
       </c>
       <c r="F27" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
@@ -1286,7 +1286,7 @@
         <v>77</v>
       </c>
       <c r="F28" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
@@ -1308,7 +1308,7 @@
         <v>78</v>
       </c>
       <c r="F29" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
@@ -1330,7 +1330,7 @@
         <v>79</v>
       </c>
       <c r="F30" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>

--- a/element_checker_settings.xlsx
+++ b/element_checker_settings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\CODE\Elemer_checker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E48C19C-CCA6-4BE4-9D0E-F04BCF6C5983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4AEAD60-A392-4786-B5C4-0EC1B37569F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="104">
   <si>
     <t>1_1</t>
   </si>
@@ -331,6 +331,12 @@
   </si>
   <si>
     <t>SN</t>
+  </si>
+  <si>
+    <t>Tmin</t>
+  </si>
+  <si>
+    <t>Tmax</t>
   </si>
 </sst>
 </file>
@@ -387,9 +393,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -670,10 +677,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>100</v>
@@ -696,8 +703,14 @@
       <c r="H1" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -718,8 +731,14 @@
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="1">
+        <v>10</v>
+      </c>
+      <c r="J2" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -740,8 +759,14 @@
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3" s="1">
+        <v>10</v>
+      </c>
+      <c r="J3" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -762,8 +787,14 @@
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I4" s="1">
+        <v>10</v>
+      </c>
+      <c r="J4" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -784,8 +815,14 @@
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I5" s="1">
+        <v>10</v>
+      </c>
+      <c r="J5" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -806,8 +843,14 @@
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I6" s="1">
+        <v>10</v>
+      </c>
+      <c r="J6" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -828,8 +871,14 @@
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I7" s="1">
+        <v>10</v>
+      </c>
+      <c r="J7" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -850,8 +899,14 @@
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I8" s="1">
+        <v>10</v>
+      </c>
+      <c r="J8" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -872,8 +927,14 @@
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I9" s="1">
+        <v>10</v>
+      </c>
+      <c r="J9" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -894,8 +955,14 @@
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I10" s="1">
+        <v>10</v>
+      </c>
+      <c r="J10" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -916,8 +983,14 @@
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I11" s="1">
+        <v>10</v>
+      </c>
+      <c r="J11" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -938,8 +1011,14 @@
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I12" s="1">
+        <v>10</v>
+      </c>
+      <c r="J12" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -960,8 +1039,14 @@
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I13" s="1">
+        <v>10</v>
+      </c>
+      <c r="J13" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -982,8 +1067,14 @@
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I14" s="1">
+        <v>10</v>
+      </c>
+      <c r="J14" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1004,8 +1095,14 @@
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I15" s="1">
+        <v>10</v>
+      </c>
+      <c r="J15" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1026,8 +1123,14 @@
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I16" s="1">
+        <v>10</v>
+      </c>
+      <c r="J16" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1048,8 +1151,14 @@
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I17" s="1">
+        <v>10</v>
+      </c>
+      <c r="J17" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1070,8 +1179,14 @@
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I18" s="1">
+        <v>10</v>
+      </c>
+      <c r="J18" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1092,8 +1207,14 @@
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I19" s="1">
+        <v>10</v>
+      </c>
+      <c r="J19" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1114,8 +1235,14 @@
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I20" s="1">
+        <v>10</v>
+      </c>
+      <c r="J20" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1136,8 +1263,14 @@
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I21" s="1">
+        <v>10</v>
+      </c>
+      <c r="J21" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -1158,8 +1291,14 @@
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I22" s="1">
+        <v>10</v>
+      </c>
+      <c r="J22" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1180,8 +1319,14 @@
       </c>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I23" s="1">
+        <v>10</v>
+      </c>
+      <c r="J23" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1202,8 +1347,14 @@
       </c>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I24" s="1">
+        <v>10</v>
+      </c>
+      <c r="J24" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1224,8 +1375,14 @@
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I25" s="1">
+        <v>10</v>
+      </c>
+      <c r="J25" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -1246,8 +1403,14 @@
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I26" s="1">
+        <v>10</v>
+      </c>
+      <c r="J26" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -1268,8 +1431,14 @@
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I27" s="1">
+        <v>10</v>
+      </c>
+      <c r="J27" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -1290,8 +1459,14 @@
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I28" s="1">
+        <v>10</v>
+      </c>
+      <c r="J28" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -1312,8 +1487,14 @@
       </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I29" s="1">
+        <v>10</v>
+      </c>
+      <c r="J29" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1334,8 +1515,14 @@
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I30" s="1">
+        <v>10</v>
+      </c>
+      <c r="J30" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1356,8 +1543,14 @@
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I31" s="1">
+        <v>10</v>
+      </c>
+      <c r="J31" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -1378,8 +1571,14 @@
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I32" s="1">
+        <v>10</v>
+      </c>
+      <c r="J32" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -1400,8 +1599,14 @@
       </c>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I33" s="1">
+        <v>10</v>
+      </c>
+      <c r="J33" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -1422,8 +1627,14 @@
       </c>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I34" s="1">
+        <v>10</v>
+      </c>
+      <c r="J34" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -1444,8 +1655,14 @@
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I35" s="1">
+        <v>10</v>
+      </c>
+      <c r="J35" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -1466,8 +1683,14 @@
       </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I36" s="1">
+        <v>10</v>
+      </c>
+      <c r="J36" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -1488,8 +1711,14 @@
       </c>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I37" s="1">
+        <v>10</v>
+      </c>
+      <c r="J37" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -1510,8 +1739,14 @@
       </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I38" s="1">
+        <v>10</v>
+      </c>
+      <c r="J38" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -1532,8 +1767,14 @@
       </c>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I39" s="1">
+        <v>10</v>
+      </c>
+      <c r="J39" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -1554,8 +1795,14 @@
       </c>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I40" s="1">
+        <v>10</v>
+      </c>
+      <c r="J40" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -1576,8 +1823,14 @@
       </c>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I41" s="1">
+        <v>10</v>
+      </c>
+      <c r="J41" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -1598,8 +1851,14 @@
       </c>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I42" s="1">
+        <v>10</v>
+      </c>
+      <c r="J42" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -1620,8 +1879,14 @@
       </c>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I43" s="1">
+        <v>10</v>
+      </c>
+      <c r="J43" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -1642,8 +1907,14 @@
       </c>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I44" s="1">
+        <v>10</v>
+      </c>
+      <c r="J44" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -1664,8 +1935,14 @@
       </c>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I45" s="1">
+        <v>10</v>
+      </c>
+      <c r="J45" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -1686,8 +1963,14 @@
       </c>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I46" s="1">
+        <v>10</v>
+      </c>
+      <c r="J46" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -1708,8 +1991,14 @@
       </c>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I47" s="1">
+        <v>10</v>
+      </c>
+      <c r="J47" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -1730,8 +2019,14 @@
       </c>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I48" s="1">
+        <v>10</v>
+      </c>
+      <c r="J48" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -1752,6 +2047,12 @@
       </c>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
+      <c r="I49" s="1">
+        <v>10</v>
+      </c>
+      <c r="J49" s="1">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
